--- a/app/test-data/排课结果_2026年012月.xlsx
+++ b/app/test-data/排课结果_2026年012月.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E71"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -935,44 +935,44 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>27名师</v>
       </c>
       <c r="B32" t="str">
-        <v>模点5-考前线代点睛</v>
+        <v>考前抱佛脚4</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-12-09</v>
+        <v>2026-12-10</v>
       </c>
       <c r="D32" t="str">
-        <v>20:00 - 21:30</v>
+        <v>19:00 - 22:00</v>
       </c>
       <c r="E32" t="str">
-        <v>方浩</v>
+        <v>火星姐姐</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>27名师</v>
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
       </c>
       <c r="B33" t="str">
-        <v>考前抱佛脚4</v>
+        <v>模考讲评3</v>
       </c>
       <c r="C33" t="str">
         <v>2026-12-10</v>
       </c>
       <c r="D33" t="str">
-        <v>19:00 - 22:00</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E33" t="str">
-        <v>火星姐姐</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+        <v>28全程3期</v>
       </c>
       <c r="B34" t="str">
-        <v>模考讲评3</v>
+        <v>高数18-定积分的概念与性质</v>
       </c>
       <c r="C34" t="str">
         <v>2026-12-10</v>
@@ -981,21 +981,21 @@
         <v>19:00 - 20:30</v>
       </c>
       <c r="E34" t="str">
-        <v>石磊</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>28全程3期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期</v>
       </c>
       <c r="B35" t="str">
-        <v>高数18-定积分的概念与性质</v>
+        <v>高数20-变限积分及其求导法则</v>
       </c>
       <c r="C35" t="str">
-        <v>2026-12-10</v>
+        <v>2026-12-11</v>
       </c>
       <c r="D35" t="str">
-        <v>19:00 - 20:30</v>
+        <v>17:30 - 18:40</v>
       </c>
       <c r="E35" t="str">
         <v>王喆</v>
@@ -1003,84 +1003,84 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期</v>
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
       <c r="B36" t="str">
-        <v>高数20-变限积分及其求导法则</v>
+        <v>临考点睛</v>
       </c>
       <c r="C36" t="str">
         <v>2026-12-11</v>
       </c>
       <c r="D36" t="str">
-        <v>17:30 - 18:40</v>
+        <v>19:00 - 22:00</v>
       </c>
       <c r="E36" t="str">
-        <v>王喆</v>
+        <v>火星姐姐</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B37" t="str">
-        <v>临考点睛</v>
+        <v>马原政经部分预热串讲5</v>
       </c>
       <c r="C37" t="str">
         <v>2026-12-11</v>
       </c>
       <c r="D37" t="str">
-        <v>19:00 - 22:00</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E37" t="str">
-        <v>火星姐姐</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B38" t="str">
-        <v>马原政经部分预热串讲5</v>
+        <v>线代7-线性方程组的求解1</v>
       </c>
       <c r="C38" t="str">
         <v>2026-12-11</v>
       </c>
       <c r="D38" t="str">
-        <v>19:00 - 21:00</v>
+        <v>20:00 - 22:00</v>
       </c>
       <c r="E38" t="str">
-        <v>石磊</v>
+        <v>方浩</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
       </c>
       <c r="B39" t="str">
-        <v>线代7-线性方程组的求解1</v>
+        <v>模点4-考前高数/线代/概率点睛</v>
       </c>
       <c r="C39" t="str">
-        <v>2026-12-11</v>
+        <v>2026-12-12</v>
       </c>
       <c r="D39" t="str">
-        <v>20:00 - 22:00</v>
+        <v>14:00 - 16:10</v>
       </c>
       <c r="E39" t="str">
-        <v>方浩</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+        <v>28全程3期</v>
       </c>
       <c r="B40" t="str">
-        <v>模点4-考前高数/线代/概率点睛</v>
+        <v>高数19-定积分的计算</v>
       </c>
       <c r="C40" t="str">
         <v>2026-12-12</v>
       </c>
       <c r="D40" t="str">
-        <v>14:00 - 16:10</v>
+        <v>18:30 - 21:00</v>
       </c>
       <c r="E40" t="str">
         <v>王喆</v>
@@ -1088,237 +1088,237 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>28全程3期</v>
+        <v>27名师,27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
       <c r="B41" t="str">
-        <v>高数19-定积分的计算</v>
+        <v>肖四套卷讲解1</v>
       </c>
       <c r="C41" t="str">
         <v>2026-12-12</v>
       </c>
       <c r="D41" t="str">
-        <v>18:30 - 21:00</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E41" t="str">
-        <v>王喆</v>
+        <v>火星姐姐</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>27名师,27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B42" t="str">
-        <v>肖四套卷讲解1</v>
+        <v>高数13-凹凸性和拐点、微分不等式</v>
       </c>
       <c r="C42" t="str">
         <v>2026-12-12</v>
       </c>
       <c r="D42" t="str">
-        <v>19:00 - 20:30</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E42" t="str">
-        <v>火星姐姐</v>
+        <v>窦峥</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+        <v>27名师,27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
       <c r="B43" t="str">
-        <v>高数13-凹凸性和拐点、微分不等式</v>
+        <v>肖四套卷讲解2</v>
       </c>
       <c r="C43" t="str">
-        <v>2026-12-12</v>
+        <v>2026-12-13</v>
       </c>
       <c r="D43" t="str">
-        <v>19:00 - 21:00</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E43" t="str">
-        <v>窦峥</v>
+        <v>火星姐姐</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>27名师,27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
       <c r="B44" t="str">
-        <v>肖四套卷讲解2</v>
+        <v>考前预测</v>
       </c>
       <c r="C44" t="str">
-        <v>2026-12-13</v>
+        <v>2026-12-14</v>
       </c>
       <c r="D44" t="str">
-        <v>19:00 - 20:30</v>
+        <v>16:30 - 18:30</v>
       </c>
       <c r="E44" t="str">
-        <v>火星姐姐</v>
+        <v>孔昱力</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>27名师,27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
       <c r="B45" t="str">
-        <v>考前预测</v>
+        <v>肖四套卷讲解3</v>
       </c>
       <c r="C45" t="str">
         <v>2026-12-14</v>
       </c>
       <c r="D45" t="str">
-        <v>16:30 - 18:30</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E45" t="str">
-        <v>孔昱力</v>
+        <v>火星姐姐</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>27名师,27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>28全程3期</v>
       </c>
       <c r="B46" t="str">
-        <v>肖四套卷讲解3</v>
+        <v>高数20-变限积分及其求导法则</v>
       </c>
       <c r="C46" t="str">
         <v>2026-12-14</v>
       </c>
       <c r="D46" t="str">
-        <v>19:00 - 20:30</v>
+        <v>19:00 - 20:10</v>
       </c>
       <c r="E46" t="str">
-        <v>火星姐姐</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>28全程3期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B47" t="str">
-        <v>高数20-变限积分及其求导法则</v>
+        <v>线代11-向量的线性表出与非齐次线性方程组</v>
       </c>
       <c r="C47" t="str">
         <v>2026-12-14</v>
       </c>
       <c r="D47" t="str">
-        <v>19:00 - 20:10</v>
+        <v>20:30 - 22:00</v>
       </c>
       <c r="E47" t="str">
-        <v>王喆</v>
+        <v>窦峥</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+        <v>27名师,27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
       </c>
       <c r="B48" t="str">
-        <v>线代11-向量的线性表出与非齐次线性方程组</v>
+        <v>肖四套卷讲解4</v>
       </c>
       <c r="C48" t="str">
-        <v>2026-12-14</v>
+        <v>2026-12-15</v>
       </c>
       <c r="D48" t="str">
-        <v>20:30 - 22:00</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E48" t="str">
-        <v>窦峥</v>
+        <v>火星姐姐</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>27名师,27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲,27OMO1期,27OMO2期,27OMO3期,27OMO4期,27OMO5期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B49" t="str">
-        <v>肖四套卷讲解4</v>
+        <v>马原政经部分预热串讲6</v>
       </c>
       <c r="C49" t="str">
         <v>2026-12-15</v>
       </c>
       <c r="D49" t="str">
-        <v>19:00 - 20:30</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E49" t="str">
-        <v>火星姐姐</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+        <v>28全程4期</v>
       </c>
       <c r="B50" t="str">
-        <v>马原政经部分预热串讲6</v>
+        <v>数学全程复习规划</v>
       </c>
       <c r="C50" t="str">
         <v>2026-12-15</v>
       </c>
       <c r="D50" t="str">
-        <v>19:00 - 21:00</v>
+        <v>19:00 - 19:30</v>
       </c>
       <c r="E50" t="str">
-        <v>石磊</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>28全程4期</v>
+        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
       </c>
       <c r="B51" t="str">
-        <v>数学全程复习规划</v>
+        <v>梦之卷</v>
       </c>
       <c r="C51" t="str">
-        <v>2026-12-15</v>
+        <v>2026-12-16</v>
       </c>
       <c r="D51" t="str">
-        <v>19:00 - 19:30</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E51" t="str">
-        <v>王喆</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>27早鸟,27早鸟暑期,27早鸟暑期强基,27全程1期,27全程2期,27全程3期,27全程4期,27全程寒假抢跑,27全程寒假特训,27全程培优,27智学1期,27智学2期,27智学3期,27暑期抢跑,27暑期超越,27百日,27新大纲</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B52" t="str">
-        <v>梦之卷</v>
+        <v>毛特&amp;习概论预热6</v>
       </c>
       <c r="C52" t="str">
         <v>2026-12-16</v>
       </c>
       <c r="D52" t="str">
-        <v>19:00 - 20:30</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E52" t="str">
-        <v>石磊</v>
+        <v>孔昱力</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+        <v>28全程4期</v>
       </c>
       <c r="B53" t="str">
-        <v>毛特&amp;习概论预热6</v>
+        <v>高数1-函数及其四个特性</v>
       </c>
       <c r="C53" t="str">
-        <v>2026-12-16</v>
+        <v>2026-12-18</v>
       </c>
       <c r="D53" t="str">
-        <v>19:00 - 21:00</v>
+        <v>16:30 - 18:30</v>
       </c>
       <c r="E53" t="str">
-        <v>孔昱力</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>28全程4期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B54" t="str">
-        <v>高数1-函数及其四个特性</v>
+        <v>高数21-反常积分</v>
       </c>
       <c r="C54" t="str">
         <v>2026-12-18</v>
       </c>
       <c r="D54" t="str">
-        <v>16:30 - 18:30</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E54" t="str">
         <v>王喆</v>
@@ -1326,95 +1326,95 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B55" t="str">
-        <v>高数21-反常积分</v>
+        <v>高数14-不定积分计算1</v>
       </c>
       <c r="C55" t="str">
-        <v>2026-12-18</v>
+        <v>2026-12-19</v>
       </c>
       <c r="D55" t="str">
-        <v>19:00 - 20:30</v>
+        <v>19:00 - 21:40</v>
       </c>
       <c r="E55" t="str">
-        <v>王喆</v>
+        <v>窦峥</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+        <v>28全程4期</v>
       </c>
       <c r="B56" t="str">
-        <v>高数14-不定积分计算1</v>
+        <v>线代1-行列式的概念及性质</v>
       </c>
       <c r="C56" t="str">
         <v>2026-12-19</v>
       </c>
       <c r="D56" t="str">
-        <v>19:00 - 21:40</v>
+        <v>19:00 - 20:50</v>
       </c>
       <c r="E56" t="str">
-        <v>窦峥</v>
+        <v>李良</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>28全程4期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B57" t="str">
-        <v>线代1-行列式的概念及性质</v>
+        <v>马原政经部分预热串讲7</v>
       </c>
       <c r="C57" t="str">
-        <v>2026-12-19</v>
+        <v>2026-12-21</v>
       </c>
       <c r="D57" t="str">
-        <v>19:00 - 20:50</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E57" t="str">
-        <v>李良</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>28全程3期</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B58" t="str">
-        <v>雷必雷技巧导学</v>
+        <v>线代8-线性方程组的求解2</v>
       </c>
       <c r="C58" t="str">
         <v>2026-12-21</v>
       </c>
       <c r="D58" t="str">
-        <v>19:00 - 21:00</v>
+        <v>20:00 - 21:40</v>
       </c>
       <c r="E58" t="str">
-        <v>石磊</v>
+        <v>方浩</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+        <v>28全程3期</v>
       </c>
       <c r="B59" t="str">
-        <v>线代8-线性方程组的求解2</v>
+        <v>雷必雷技巧导学</v>
       </c>
       <c r="C59" t="str">
-        <v>2026-12-21</v>
+        <v>2026-12-22</v>
       </c>
       <c r="D59" t="str">
-        <v>20:00 - 21:40</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E59" t="str">
-        <v>方浩</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B60" t="str">
-        <v>马原政经部分预热串讲7</v>
+        <v>毛特&amp;习概论预热7</v>
       </c>
       <c r="C60" t="str">
         <v>2026-12-22</v>
@@ -1423,38 +1423,38 @@
         <v>19:00 - 21:00</v>
       </c>
       <c r="E60" t="str">
-        <v>石磊</v>
+        <v>孔昱力</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+        <v>28全程4期</v>
       </c>
       <c r="B61" t="str">
-        <v>毛特&amp;习概论预热7</v>
+        <v>高数2-极限的定义与性质</v>
       </c>
       <c r="C61" t="str">
         <v>2026-12-22</v>
       </c>
       <c r="D61" t="str">
-        <v>19:00 - 21:00</v>
+        <v>19:00 - 20:40</v>
       </c>
       <c r="E61" t="str">
-        <v>孔昱力</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>28全程4期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B62" t="str">
-        <v>高数2-极限的定义与性质</v>
+        <v>高数22-定积分的几何应用1</v>
       </c>
       <c r="C62" t="str">
-        <v>2026-12-22</v>
+        <v>2026-12-23</v>
       </c>
       <c r="D62" t="str">
-        <v>19:00 - 20:40</v>
+        <v>19:00 - 20:00</v>
       </c>
       <c r="E62" t="str">
         <v>王喆</v>
@@ -1462,112 +1462,112 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+        <v>28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B63" t="str">
-        <v>高数22-定积分的几何应用1</v>
+        <v>线代10-非齐次线性方程组解的判定与求解</v>
       </c>
       <c r="C63" t="str">
         <v>2026-12-23</v>
       </c>
       <c r="D63" t="str">
-        <v>19:00 - 20:00</v>
+        <v>20:30 - 22:00</v>
       </c>
       <c r="E63" t="str">
-        <v>王喆</v>
+        <v>李良</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B64" t="str">
-        <v>线代10-非齐次线性方程组解的判定与求解</v>
+        <v>线代12-特征值与特征向量的概念与性质</v>
       </c>
       <c r="C64" t="str">
-        <v>2026-12-23</v>
+        <v>2026-12-24</v>
       </c>
       <c r="D64" t="str">
-        <v>20:30 - 22:00</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E64" t="str">
-        <v>李良</v>
+        <v>窦峥</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+        <v>28全程4期</v>
       </c>
       <c r="B65" t="str">
-        <v>线代12-特征值与特征向量的概念与性质</v>
+        <v>高数3-无穷小、无穷大及其阶</v>
       </c>
       <c r="C65" t="str">
-        <v>2026-12-24</v>
+        <v>2026-12-25</v>
       </c>
       <c r="D65" t="str">
-        <v>19:00 - 20:30</v>
+        <v>19:00 - 20:15</v>
       </c>
       <c r="E65" t="str">
-        <v>窦峥</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>28全程4期</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B66" t="str">
-        <v>高数3-无穷小、无穷大及其阶</v>
+        <v>高数15-不定积分计算2</v>
       </c>
       <c r="C66" t="str">
-        <v>2026-12-25</v>
+        <v>2026-12-27</v>
       </c>
       <c r="D66" t="str">
-        <v>19:00 - 20:15</v>
+        <v>19:00 - 20:40</v>
       </c>
       <c r="E66" t="str">
-        <v>王喆</v>
+        <v>窦峥</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+        <v>28全程4期</v>
       </c>
       <c r="B67" t="str">
-        <v>高数15-不定积分计算2</v>
+        <v>线代2-行列式的展开定理与克拉默法则</v>
       </c>
       <c r="C67" t="str">
         <v>2026-12-27</v>
       </c>
       <c r="D67" t="str">
-        <v>19:00 - 20:40</v>
+        <v>19:00 - 20:30</v>
       </c>
       <c r="E67" t="str">
-        <v>窦峥</v>
+        <v>李良</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>28全程4期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B68" t="str">
-        <v>线代2-行列式的展开定理与克拉默法则</v>
+        <v>马原政经部分预热串讲8</v>
       </c>
       <c r="C68" t="str">
-        <v>2026-12-27</v>
+        <v>2026-12-28</v>
       </c>
       <c r="D68" t="str">
-        <v>19:00 - 20:30</v>
+        <v>19:00 - 21:00</v>
       </c>
       <c r="E68" t="str">
-        <v>李良</v>
+        <v>石磊</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
+        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
       </c>
       <c r="B69" t="str">
-        <v>马原政经部分预热串讲8</v>
+        <v>毛特&amp;习概论预热8</v>
       </c>
       <c r="C69" t="str">
         <v>2026-12-28</v>
@@ -1576,15 +1576,15 @@
         <v>19:00 - 21:00</v>
       </c>
       <c r="E69" t="str">
-        <v>石磊</v>
+        <v>孔昱力</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>28OMO1期,28OMO2期,28OMO3期,28OMO4期</v>
+        <v>28全程4期</v>
       </c>
       <c r="B70" t="str">
-        <v>毛特&amp;习概论预热8</v>
+        <v>高数4-函数极限的计算1</v>
       </c>
       <c r="C70" t="str">
         <v>2026-12-28</v>
@@ -1593,46 +1593,29 @@
         <v>19:00 - 21:00</v>
       </c>
       <c r="E70" t="str">
-        <v>孔昱力</v>
+        <v>王喆</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>28全程4期</v>
+        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
       </c>
       <c r="B71" t="str">
-        <v>高数4-函数极限的计算1</v>
+        <v>高数23-定积分的几何应用2</v>
       </c>
       <c r="C71" t="str">
-        <v>2026-12-28</v>
+        <v>2026-12-29</v>
       </c>
       <c r="D71" t="str">
-        <v>19:00 - 21:00</v>
+        <v>19:00 - 20:00</v>
       </c>
       <c r="E71" t="str">
-        <v>王喆</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>28早鸟1期,28早鸟2期,28早鸟3期,28早鸟4期,28早鸟5期,28全程1期,28全程2期,28全程3期</v>
-      </c>
-      <c r="B72" t="str">
-        <v>高数23-定积分的几何应用2</v>
-      </c>
-      <c r="C72" t="str">
-        <v>2026-12-29</v>
-      </c>
-      <c r="D72" t="str">
-        <v>19:00 - 20:00</v>
-      </c>
-      <c r="E72" t="str">
         <v>王喆</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E71"/>
   </ignoredErrors>
 </worksheet>
 </file>